--- a/content/athena-class-schedule.xlsx
+++ b/content/athena-class-schedule.xlsx
@@ -1095,7 +1095,7 @@
       <formula1>"Open,Pending,Full,Cancelled"</formula1>
     </dataValidation>
     <dataValidation sqref="A2:A500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"DUI Risk Reduction (RRP),Driver Improvement"</formula1>
+      <formula1>"DUI Risk Reduction (RRP),Driver Improvement,Family Enrichment"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
